--- a/src/nodes/HPC/compressor_stage_1_blade_rotor_coordinates_lattice.xlsx
+++ b/src/nodes/HPC/compressor_stage_1_blade_rotor_coordinates_lattice.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\projects\gte\src\nodes\HPC\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="600" yWindow="210" windowWidth="15135" windowHeight="6720"/>
+    <workbookView xWindow="600" yWindow="216" windowWidth="15132" windowHeight="6720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,9 +20,497 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="161">
+  <si>
+    <t>-19.2149570359165</t>
+  </si>
+  <si>
+    <t>15.5473448514592</t>
+  </si>
+  <si>
+    <t>182.168420475777</t>
+  </si>
+  <si>
+    <t>-17.1728776902364</t>
+  </si>
+  <si>
+    <t>15.62580959791</t>
+  </si>
+  <si>
+    <t>-15.6514512899292</t>
+  </si>
+  <si>
+    <t>15.2045551447825</t>
+  </si>
+  <si>
+    <t>-14.2161177720786</t>
+  </si>
+  <si>
+    <t>14.7006693213862</t>
+  </si>
+  <si>
+    <t>-12.8425575466197</t>
+  </si>
+  <si>
+    <t>14.1374939069031</t>
+  </si>
+  <si>
+    <t>-11.5207644108359</t>
+  </si>
+  <si>
+    <t>13.5246327874858</t>
+  </si>
+  <si>
+    <t>-10.2449729623491</t>
+  </si>
+  <si>
+    <t>12.8676195576088</t>
+  </si>
+  <si>
+    <t>-9.01174048975304</t>
+  </si>
+  <si>
+    <t>12.1697585085539</t>
+  </si>
+  <si>
+    <t>-7.81577926754523</t>
+  </si>
+  <si>
+    <t>11.4361247637391</t>
+  </si>
+  <si>
+    <t>-6.65139768148118</t>
+  </si>
+  <si>
+    <t>10.6721810962839</t>
+  </si>
+  <si>
+    <t>-5.51313357644527</t>
+  </si>
+  <si>
+    <t>9.88317004597735</t>
+  </si>
+  <si>
+    <t>-4.39803053364503</t>
+  </si>
+  <si>
+    <t>9.07192916371714</t>
+  </si>
+  <si>
+    <t>-3.31292562045161</t>
+  </si>
+  <si>
+    <t>8.23189627816724</t>
+  </si>
+  <si>
+    <t>-2.26188159697026</t>
+  </si>
+  <si>
+    <t>7.35917197946946</t>
+  </si>
+  <si>
+    <t>-1.22807050807894</t>
+  </si>
+  <si>
+    <t>6.46990762591125</t>
+  </si>
+  <si>
+    <t>-0.196058175172618</t>
+  </si>
+  <si>
+    <t>5.57891683844145</t>
+  </si>
+  <si>
+    <t>0.823123759058402</t>
+  </si>
+  <si>
+    <t>4.67561152050893</t>
+  </si>
+  <si>
+    <t>1.81520875687362</t>
+  </si>
+  <si>
+    <t>3.74629874502322</t>
+  </si>
+  <si>
+    <t>2.77945652162714</t>
+  </si>
+  <si>
+    <t>2.7902679802364</t>
+  </si>
+  <si>
+    <t>3.7185083169467</t>
+  </si>
+  <si>
+    <t>1.81005429323615</t>
+  </si>
+  <si>
+    <t>4.63500540646004</t>
+  </si>
+  <si>
+    <t>0.808192751110197</t>
+  </si>
+  <si>
+    <t>5.53111619648142</t>
+  </si>
+  <si>
+    <t>-0.213235424326927</t>
+  </si>
+  <si>
+    <t>6.40711766407109</t>
+  </si>
+  <si>
+    <t>-1.25396439235334</t>
+  </si>
+  <si>
+    <t>7.26281392897579</t>
+  </si>
+  <si>
+    <t>-2.3141821575203</t>
+  </si>
+  <si>
+    <t>8.09800911094228</t>
+  </si>
+  <si>
+    <t>-3.39407672437909</t>
+  </si>
+  <si>
+    <t>8.91242449924425</t>
+  </si>
+  <si>
+    <t>-4.49391559761266</t>
+  </si>
+  <si>
+    <t>9.70545006126305</t>
+  </si>
+  <si>
+    <t>-5.61428428243058</t>
+  </si>
+  <si>
+    <t>10.476392933907</t>
+  </si>
+  <si>
+    <t>-6.75584778417407</t>
+  </si>
+  <si>
+    <t>11.2245602540844</t>
+  </si>
+  <si>
+    <t>-7.9192711081844</t>
+  </si>
+  <si>
+    <t>11.9496006071157</t>
+  </si>
+  <si>
+    <t>-9.10489153991034</t>
+  </si>
+  <si>
+    <t>12.6525283719704</t>
+  </si>
+  <si>
+    <t>-10.3117354852309</t>
+  </si>
+  <si>
+    <t>13.3346993760303</t>
+  </si>
+  <si>
+    <t>-11.5385016301327</t>
+  </si>
+  <si>
+    <t>13.9974694466769</t>
+  </si>
+  <si>
+    <t>-12.7838886606023</t>
+  </si>
+  <si>
+    <t>14.6416248496004</t>
+  </si>
+  <si>
+    <t>-14.047141924112</t>
+  </si>
+  <si>
+    <t>15.2656736037245</t>
+  </si>
+  <si>
+    <t>-15.3296934140766</t>
+  </si>
+  <si>
+    <t>15.8675541662813</t>
+  </si>
+  <si>
+    <t>-16.6335217853967</t>
+  </si>
+  <si>
+    <t>16.4452049945029</t>
+  </si>
+  <si>
+    <t>-17.960605692973</t>
+  </si>
+  <si>
+    <t>16.9951783752931</t>
+  </si>
+  <si>
+    <t>-19.3142542286757</t>
+  </si>
+  <si>
+    <t>17.5084819142428</t>
+  </si>
+  <si>
+    <t>-20.703098232254</t>
+  </si>
+  <si>
+    <t>17.9747370466145</t>
+  </si>
+  <si>
+    <t>-22.1370989804269</t>
+  </si>
+  <si>
+    <t>18.3835652076706</t>
+  </si>
+  <si>
+    <t>-23.6262177499133</t>
+  </si>
+  <si>
+    <t>17.4933387376264</t>
+  </si>
+  <si>
+    <t>-22.599141843689</t>
+  </si>
+  <si>
+    <t>16.6283616485653</t>
+  </si>
+  <si>
+    <t>-21.5478317512051</t>
+  </si>
+  <si>
+    <t>15.7786377868873</t>
+  </si>
+  <si>
+    <t>-20.4818817135396</t>
+  </si>
+  <si>
+    <t>14.9341709989926</t>
+  </si>
+  <si>
+    <t>-19.4108859717704</t>
+  </si>
+  <si>
+    <t>14.0863350952963</t>
+  </si>
+  <si>
+    <t>-18.3431238847162</t>
+  </si>
+  <si>
+    <t>13.231983742273</t>
+  </si>
+  <si>
+    <t>-17.2816152821596</t>
+  </si>
+  <si>
+    <t>12.3693405704128</t>
+  </si>
+  <si>
+    <t>-16.228065111624</t>
+  </si>
+  <si>
+    <t>11.4966292102053</t>
+  </si>
+  <si>
+    <t>-15.1841783206329</t>
+  </si>
+  <si>
+    <t>10.6126271890528</t>
+  </si>
+  <si>
+    <t>-14.1511282301739</t>
+  </si>
+  <si>
+    <t>9.71832762200719</t>
+  </si>
+  <si>
+    <t>-13.1279616550911</t>
+  </si>
+  <si>
+    <t>8.81527752103286</t>
+  </si>
+  <si>
+    <t>-12.1131937836931</t>
+  </si>
+  <si>
+    <t>7.90502389809414</t>
+  </si>
+  <si>
+    <t>-11.1053398042882</t>
+  </si>
+  <si>
+    <t>6.9887589818315</t>
+  </si>
+  <si>
+    <t>-10.1032554238358</t>
+  </si>
+  <si>
+    <t>6.06625586759006</t>
+  </si>
+  <si>
+    <t>-9.10715842389948</t>
+  </si>
+  <si>
+    <t>5.13693286739102</t>
+  </si>
+  <si>
+    <t>-8.11760710469394</t>
+  </si>
+  <si>
+    <t>4.20020829325564</t>
+  </si>
+  <si>
+    <t>-7.13515976643381</t>
+  </si>
+  <si>
+    <t>3.25557091291224</t>
+  </si>
+  <si>
+    <t>-6.16030708641931</t>
+  </si>
+  <si>
+    <t>2.30279131691746</t>
+  </si>
+  <si>
+    <t>-5.19326925029315</t>
+  </si>
+  <si>
+    <t>1.34171055153506</t>
+  </si>
+  <si>
+    <t>-4.23419882078366</t>
+  </si>
+  <si>
+    <t>0.37216966302877</t>
+  </si>
+  <si>
+    <t>-3.28324836061916</t>
+  </si>
+  <si>
+    <t>-0.605530006327272</t>
+  </si>
+  <si>
+    <t>-2.34012864350914</t>
+  </si>
+  <si>
+    <t>-1.58924593021737</t>
+  </si>
+  <si>
+    <t>-1.40278328708781</t>
+  </si>
+  <si>
+    <t>-2.57637528631541</t>
+  </si>
+  <si>
+    <t>-0.468714119970579</t>
+  </si>
+  <si>
+    <t>-3.56431525229532</t>
+  </si>
+  <si>
+    <t>0.464577029227174</t>
+  </si>
+  <si>
+    <t>-4.55385482776736</t>
+  </si>
+  <si>
+    <t>1.39633288397946</t>
+  </si>
+  <si>
+    <t>-5.55935030008733</t>
+  </si>
+  <si>
+    <t>2.3127743761179</t>
+  </si>
+  <si>
+    <t>-6.59193810977239</t>
+  </si>
+  <si>
+    <t>3.20321282484113</t>
+  </si>
+  <si>
+    <t>-7.63630802223957</t>
+  </si>
+  <si>
+    <t>4.08234289045819</t>
+  </si>
+  <si>
+    <t>-8.67576796308454</t>
+  </si>
+  <si>
+    <t>4.96618551385642</t>
+  </si>
+  <si>
+    <t>-9.71454517371759</t>
+  </si>
+  <si>
+    <t>5.85068341712594</t>
+  </si>
+  <si>
+    <t>-10.7596553597618</t>
+  </si>
+  <si>
+    <t>6.72910297313638</t>
+  </si>
+  <si>
+    <t>-11.8083487678771</t>
+  </si>
+  <si>
+    <t>7.60408337667269</t>
+  </si>
+  <si>
+    <t>-12.8553844602072</t>
+  </si>
+  <si>
+    <t>8.48065484468419</t>
+  </si>
+  <si>
+    <t>-13.8953222197954</t>
+  </si>
+  <si>
+    <t>9.36403886086239</t>
+  </si>
+  <si>
+    <t>-14.9231417918853</t>
+  </si>
+  <si>
+    <t>10.2590538319996</t>
+  </si>
+  <si>
+    <t>-15.9357020496241</t>
+  </si>
+  <si>
+    <t>11.1687145905495</t>
+  </si>
+  <si>
+    <t>-16.9275550810952</t>
+  </si>
+  <si>
+    <t>12.0982500057741</t>
+  </si>
+  <si>
+    <t>-17.8890451857196</t>
+  </si>
+  <si>
+    <t>13.0569275542288</t>
+  </si>
+  <si>
+    <t>-18.7962301244373</t>
+  </si>
+  <si>
+    <t>14.0677268361357</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -45,21 +538,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -97,9 +599,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -131,9 +633,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -165,9 +668,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -340,923 +844,927 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C82"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1">
-        <v>-19.214957035916488</v>
-      </c>
-      <c r="B1">
-        <v>15.547344851459163</v>
-      </c>
-      <c r="C1">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
-        <v>-17.172877690236444</v>
-      </c>
-      <c r="B2">
-        <v>15.625809597909973</v>
-      </c>
-      <c r="C2">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>-15.651451289929165</v>
-      </c>
-      <c r="B3">
-        <v>15.204555144782525</v>
-      </c>
-      <c r="C3">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
-        <v>-14.216117772078622</v>
-      </c>
-      <c r="B4">
-        <v>14.700669321386213</v>
-      </c>
-      <c r="C4">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5">
-        <v>-12.842557546619741</v>
-      </c>
-      <c r="B5">
-        <v>14.137493906903135</v>
-      </c>
-      <c r="C5">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6">
-        <v>-11.520764410835929</v>
-      </c>
-      <c r="B6">
-        <v>13.524632787485837</v>
-      </c>
-      <c r="C6">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7">
-        <v>-10.244972962349072</v>
-      </c>
-      <c r="B7">
-        <v>12.867619557608808</v>
-      </c>
-      <c r="C7">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8">
-        <v>-9.011740489753036</v>
-      </c>
-      <c r="B8">
-        <v>12.169758508553871</v>
-      </c>
-      <c r="C8">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9">
-        <v>-7.8157792675452313</v>
-      </c>
-      <c r="B9">
-        <v>11.436124763739082</v>
-      </c>
-      <c r="C9">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10">
-        <v>-6.6513976814811757</v>
-      </c>
-      <c r="B10">
-        <v>10.672181096283932</v>
-      </c>
-      <c r="C10">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11">
-        <v>-5.5131335764452682</v>
-      </c>
-      <c r="B11">
-        <v>9.8831700459773462</v>
-      </c>
-      <c r="C11">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12">
-        <v>-4.3980305336450281</v>
-      </c>
-      <c r="B12">
-        <v>9.0719291637171438</v>
-      </c>
-      <c r="C12">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13">
-        <v>-3.3129256204516113</v>
-      </c>
-      <c r="B13">
-        <v>8.2318962781672358</v>
-      </c>
-      <c r="C13">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14">
-        <v>-2.2618815969702633</v>
-      </c>
-      <c r="B14">
-        <v>7.3591719794694583</v>
-      </c>
-      <c r="C14">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15">
-        <v>-1.2280705080789405</v>
-      </c>
-      <c r="B15">
-        <v>6.4699076259112456</v>
-      </c>
-      <c r="C15">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16">
-        <v>-0.19605817517261842</v>
-      </c>
-      <c r="B16">
-        <v>5.5789168384414465</v>
-      </c>
-      <c r="C16">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17">
-        <v>0.82312375905840229</v>
-      </c>
-      <c r="B17">
-        <v>4.6756115205089293</v>
-      </c>
-      <c r="C17">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18">
-        <v>1.8152087568736208</v>
-      </c>
-      <c r="B18">
-        <v>3.7462987450232221</v>
-      </c>
-      <c r="C18">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19">
-        <v>2.7794565216271363</v>
-      </c>
-      <c r="B19">
-        <v>2.7902679802363966</v>
-      </c>
-      <c r="C19">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20">
-        <v>3.7185083169466986</v>
-      </c>
-      <c r="B20">
-        <v>1.8100542932361496</v>
-      </c>
-      <c r="C20">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21">
-        <v>4.6350054064600439</v>
-      </c>
-      <c r="B21">
-        <v>0.80819275111019739</v>
-      </c>
-      <c r="C21">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22">
-        <v>5.5311161964814222</v>
-      </c>
-      <c r="B22">
-        <v>-0.21323542432692688</v>
-      </c>
-      <c r="C22">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23">
-        <v>6.4071176640710883</v>
-      </c>
-      <c r="B23">
-        <v>-1.253964392353335</v>
-      </c>
-      <c r="C23">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24">
-        <v>7.2628139289757909</v>
-      </c>
-      <c r="B24">
-        <v>-2.3141821575202974</v>
-      </c>
-      <c r="C24">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25">
-        <v>8.098009110942284</v>
-      </c>
-      <c r="B25">
-        <v>-3.3940767243790941</v>
-      </c>
-      <c r="C25">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26">
-        <v>8.9124244992442474</v>
-      </c>
-      <c r="B26">
-        <v>-4.4939155976126566</v>
-      </c>
-      <c r="C26">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27">
-        <v>9.7054500612630523</v>
-      </c>
-      <c r="B27">
-        <v>-5.6142842824305754</v>
-      </c>
-      <c r="C27">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28">
-        <v>10.476392933906991</v>
-      </c>
-      <c r="B28">
-        <v>-6.7558477841740716</v>
-      </c>
-      <c r="C28">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29">
-        <v>11.224560254084363</v>
-      </c>
-      <c r="B29">
-        <v>-7.9192711081843994</v>
-      </c>
-      <c r="C29">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30">
-        <v>11.94960060711569</v>
-      </c>
-      <c r="B30">
-        <v>-9.1048915399103389</v>
-      </c>
-      <c r="C30">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31">
-        <v>12.65252837197043</v>
-      </c>
-      <c r="B31">
-        <v>-10.311735485230916</v>
-      </c>
-      <c r="C31">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32">
-        <v>13.334699376030272</v>
-      </c>
-      <c r="B32">
-        <v>-11.538501630132718</v>
-      </c>
-      <c r="C32">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33">
-        <v>13.9974694466769</v>
-      </c>
-      <c r="B33">
-        <v>-12.783888660602317</v>
-      </c>
-      <c r="C33">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34">
-        <v>14.641624849600401</v>
-      </c>
-      <c r="B34">
-        <v>-14.047141924111953</v>
-      </c>
-      <c r="C34">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35">
-        <v>15.26567360372449</v>
-      </c>
-      <c r="B35">
-        <v>-15.329693414076557</v>
-      </c>
-      <c r="C35">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36">
-        <v>15.867554166281275</v>
-      </c>
-      <c r="B36">
-        <v>-16.633521785396695</v>
-      </c>
-      <c r="C36">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37">
-        <v>16.445204994502863</v>
-      </c>
-      <c r="B37">
-        <v>-17.960605692972962</v>
-      </c>
-      <c r="C37">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38">
-        <v>16.995178375293115</v>
-      </c>
-      <c r="B38">
-        <v>-19.314254228675672</v>
-      </c>
-      <c r="C38">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39">
-        <v>17.508481914242811</v>
-      </c>
-      <c r="B39">
-        <v>-20.703098232254018</v>
-      </c>
-      <c r="C39">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40">
-        <v>17.974737046614468</v>
-      </c>
-      <c r="B40">
-        <v>-22.137098980426931</v>
-      </c>
-      <c r="C40">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41">
-        <v>18.383565207670614</v>
-      </c>
-      <c r="B41">
-        <v>-23.626217749913337</v>
-      </c>
-      <c r="C41">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42">
-        <v>18.383565207670614</v>
-      </c>
-      <c r="B42">
-        <v>-23.626217749913337</v>
-      </c>
-      <c r="C42">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43">
-        <v>17.493338737626377</v>
-      </c>
-      <c r="B43">
-        <v>-22.599141843688994</v>
-      </c>
-      <c r="C43">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44">
-        <v>16.628361648565257</v>
-      </c>
-      <c r="B44">
-        <v>-21.547831751205138</v>
-      </c>
-      <c r="C44">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45">
-        <v>15.778637786887318</v>
-      </c>
-      <c r="B45">
-        <v>-20.481881713539643</v>
-      </c>
-      <c r="C45">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46">
-        <v>14.934170998992643</v>
-      </c>
-      <c r="B46">
-        <v>-19.410885971770394</v>
-      </c>
-      <c r="C46">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47">
-        <v>14.086335095296272</v>
-      </c>
-      <c r="B47">
-        <v>-18.343123884716217</v>
-      </c>
-      <c r="C47">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48">
-        <v>13.231983742273048</v>
-      </c>
-      <c r="B48">
-        <v>-17.281615282159617</v>
-      </c>
-      <c r="C48">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49">
-        <v>12.36934057041278</v>
-      </c>
-      <c r="B49">
-        <v>-16.22806511162403</v>
-      </c>
-      <c r="C49">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50">
-        <v>11.496629210205281</v>
-      </c>
-      <c r="B50">
-        <v>-15.184178320632919</v>
-      </c>
-      <c r="C50">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51">
-        <v>10.612627189052775</v>
-      </c>
-      <c r="B51">
-        <v>-14.151128230173875</v>
-      </c>
-      <c r="C51">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52">
-        <v>9.7183276220071875</v>
-      </c>
-      <c r="B52">
-        <v>-13.127961655091138</v>
-      </c>
-      <c r="C52">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53">
-        <v>8.8152775210328613</v>
-      </c>
-      <c r="B53">
-        <v>-12.113193783693109</v>
-      </c>
-      <c r="C53">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54">
-        <v>7.9050238980941394</v>
-      </c>
-      <c r="B54">
-        <v>-11.105339804288175</v>
-      </c>
-      <c r="C54">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55">
-        <v>6.9887589818315048</v>
-      </c>
-      <c r="B55">
-        <v>-10.103255423835762</v>
-      </c>
-      <c r="C55">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56">
-        <v>6.0662558675900558</v>
-      </c>
-      <c r="B56">
-        <v>-9.1071584238994774</v>
-      </c>
-      <c r="C56">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57">
-        <v>5.1369328673910184</v>
-      </c>
-      <c r="B57">
-        <v>-8.117607104693942</v>
-      </c>
-      <c r="C57">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58">
-        <v>4.200208293255641</v>
-      </c>
-      <c r="B58">
-        <v>-7.1351597664338051</v>
-      </c>
-      <c r="C58">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59">
-        <v>3.2555709129122365</v>
-      </c>
-      <c r="B59">
-        <v>-6.160307086419305</v>
-      </c>
-      <c r="C59">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60">
-        <v>2.3027913169174634</v>
-      </c>
-      <c r="B60">
-        <v>-5.1932692502931515</v>
-      </c>
-      <c r="C60">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61">
-        <v>1.3417105515350594</v>
-      </c>
-      <c r="B61">
-        <v>-4.23419882078366</v>
-      </c>
-      <c r="C61">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62">
-        <v>0.37216966302877</v>
-      </c>
-      <c r="B62">
-        <v>-3.2832483606191554</v>
-      </c>
-      <c r="C62">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63">
-        <v>-0.60553000632727161</v>
-      </c>
-      <c r="B63">
-        <v>-2.3401286435091371</v>
-      </c>
-      <c r="C63">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64">
-        <v>-1.5892459302173689</v>
-      </c>
-      <c r="B64">
-        <v>-1.4027832870878105</v>
-      </c>
-      <c r="C64">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65">
-        <v>-2.5763752863154141</v>
-      </c>
-      <c r="B65">
-        <v>-0.46871411997057866</v>
-      </c>
-      <c r="C65">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66">
-        <v>-3.5643152522953176</v>
-      </c>
-      <c r="B66">
-        <v>0.4645770292271737</v>
-      </c>
-      <c r="C66">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67">
-        <v>-4.55385482776736</v>
-      </c>
-      <c r="B67">
-        <v>1.3963328839794584</v>
-      </c>
-      <c r="C67">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68">
-        <v>-5.5593503000873321</v>
-      </c>
-      <c r="B68">
-        <v>2.3127743761178965</v>
-      </c>
-      <c r="C68">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69">
-        <v>-6.5919381097723884</v>
-      </c>
-      <c r="B69">
-        <v>3.2032128248411307</v>
-      </c>
-      <c r="C69">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70">
-        <v>-7.6363080222395672</v>
-      </c>
-      <c r="B70">
-        <v>4.0823428904581949</v>
-      </c>
-      <c r="C70">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71">
-        <v>-8.675767963084537</v>
-      </c>
-      <c r="B71">
-        <v>4.9661855138564235</v>
-      </c>
-      <c r="C71">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72">
-        <v>-9.714545173717589</v>
-      </c>
-      <c r="B72">
-        <v>5.8506834171259374</v>
-      </c>
-      <c r="C72">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73">
-        <v>-10.759655359761842</v>
-      </c>
-      <c r="B73">
-        <v>6.729102973136377</v>
-      </c>
-      <c r="C73">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74">
-        <v>-11.808348767877115</v>
-      </c>
-      <c r="B74">
-        <v>7.6040833766726852</v>
-      </c>
-      <c r="C74">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75">
-        <v>-12.855384460207237</v>
-      </c>
-      <c r="B75">
-        <v>8.480654844684187</v>
-      </c>
-      <c r="C75">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76">
-        <v>-13.895322219795366</v>
-      </c>
-      <c r="B76">
-        <v>9.3640388608623866</v>
-      </c>
-      <c r="C76">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77">
-        <v>-14.923141791885314</v>
-      </c>
-      <c r="B77">
-        <v>10.259053831999648</v>
-      </c>
-      <c r="C77">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78">
-        <v>-15.935702049624114</v>
-      </c>
-      <c r="B78">
-        <v>11.1687145905495</v>
-      </c>
-      <c r="C78">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79">
-        <v>-16.927555081095221</v>
-      </c>
-      <c r="B79">
-        <v>12.098250005774091</v>
-      </c>
-      <c r="C79">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80">
-        <v>-17.88904518571956</v>
-      </c>
-      <c r="B80">
-        <v>13.05692755422883</v>
-      </c>
-      <c r="C80">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81">
-        <v>-18.796230124437319</v>
-      </c>
-      <c r="B81">
-        <v>14.067726836135725</v>
-      </c>
-      <c r="C81">
-        <v>182.16842047577737</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82">
-        <v>-19.214957035916488</v>
-      </c>
-      <c r="B82">
-        <v>15.547344851459163</v>
-      </c>
-      <c r="C82">
-        <v>182.16842047577737</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C82"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>-26.354322818002842</v>
       </c>
@@ -1267,7 +1775,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>-24.6840429746773</v>
       </c>
@@ -1278,7 +1786,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>-23.127659234757541</v>
       </c>
@@ -1289,7 +1797,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>-21.589706360983204</v>
       </c>
@@ -1300,7 +1808,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>-20.064877754018198</v>
       </c>
@@ -1311,7 +1819,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>-18.551009803513136</v>
       </c>
@@ -1322,7 +1830,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>-17.046867531949353</v>
       </c>
@@ -1333,18 +1841,18 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>-15.551724803881276</v>
       </c>
       <c r="B8">
-        <v>8.04071033478707</v>
+        <v>8.0407103347870699</v>
       </c>
       <c r="C8">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>-14.064446494210413</v>
       </c>
@@ -1355,7 +1863,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>-12.583807069148953</v>
       </c>
@@ -1366,7 +1874,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>-11.108628349804764</v>
       </c>
@@ -1377,7 +1885,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>-9.6382813828396241</v>
       </c>
@@ -1388,9 +1896,9 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>-8.17428676223524</v>
+        <v>-8.1742867622352406</v>
       </c>
       <c r="B13">
         <v>5.1610687985187216</v>
@@ -1399,7 +1907,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>-6.7175539185272859</v>
       </c>
@@ -1410,7 +1918,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>-5.2643980811473261</v>
       </c>
@@ -1421,7 +1929,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>-3.8114395966930816</v>
       </c>
@@ -1432,7 +1940,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>-2.3611134815309547</v>
       </c>
@@ -1443,7 +1951,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>-0.91656419861926164</v>
       </c>
@@ -1454,7 +1962,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>0.52204067248474584</v>
       </c>
@@ -1465,7 +1973,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1.9552777730740831</v>
       </c>
@@ -1476,18 +1984,18 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>3.3837237444417627</v>
       </c>
       <c r="B21">
-        <v>0.024260679723415481</v>
+        <v>2.4260679723415481E-2</v>
       </c>
       <c r="C21">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>4.8078525621905506</v>
       </c>
@@ -1498,7 +2006,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>6.2277275391621627</v>
       </c>
@@ -1509,7 +2017,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>7.6433093225080784</v>
       </c>
@@ -1520,7 +2028,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9.0545585593797551</v>
       </c>
@@ -1531,7 +2039,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>10.461418934463083</v>
       </c>
@@ -1542,7 +2050,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>11.863766282581617</v>
       </c>
@@ -1553,7 +2061,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>13.261459476093316</v>
       </c>
@@ -1564,7 +2072,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>14.654357387356152</v>
       </c>
@@ -1575,7 +2083,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>16.042395277658017</v>
       </c>
@@ -1586,7 +2094,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>17.425813964006544</v>
       </c>
@@ -1597,7 +2105,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>18.804930652339294</v>
       </c>
@@ -1608,7 +2116,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>20.180062548593828</v>
       </c>
@@ -1619,7 +2127,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>21.551403278971051</v>
       </c>
@@ -1630,9 +2138,9 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>22.9186521507252</v>
+        <v>22.918652150725201</v>
       </c>
       <c r="B35">
         <v>-10.454089704676003</v>
@@ -1641,7 +2149,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>24.281384891373865</v>
       </c>
@@ -1652,7 +2160,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>25.639177228434637</v>
       </c>
@@ -1663,7 +2171,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>26.99130190906402</v>
       </c>
@@ -1674,18 +2182,18 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>28.3358197589743</v>
+        <v>28.335819758974299</v>
       </c>
       <c r="B39">
-        <v>-13.801500364897049</v>
+        <v>-13.801500364897048</v>
       </c>
       <c r="C39">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>29.670488623516654</v>
       </c>
@@ -1696,29 +2204,29 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>30.993066348042294</v>
       </c>
       <c r="B41">
-        <v>-15.5857304840661</v>
+        <v>-15.585730484066101</v>
       </c>
       <c r="C41">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>30.993066348042294</v>
       </c>
       <c r="B42">
-        <v>-15.5857304840661</v>
+        <v>-15.585730484066101</v>
       </c>
       <c r="C42">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>29.564687982303653</v>
       </c>
@@ -1729,7 +2237,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>28.14238889992335</v>
       </c>
@@ -1740,7 +2248,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>26.723933345627387</v>
       </c>
@@ -1751,7 +2259,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>25.307085564141786</v>
       </c>
@@ -1762,7 +2270,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>23.889912556859091</v>
       </c>
@@ -1773,7 +2281,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>22.471692351838044</v>
       </c>
@@ -1784,18 +2292,18 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>21.052005733803913</v>
       </c>
       <c r="B49">
-        <v>-10.720294044477758</v>
+        <v>-10.720294044477757</v>
       </c>
       <c r="C49">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>19.630433487481966</v>
       </c>
@@ -1806,18 +2314,18 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>18.2066797290744</v>
+        <v>18.206679729074398</v>
       </c>
       <c r="B51">
-        <v>-9.34098339200246</v>
+        <v>-9.3409833920024603</v>
       </c>
       <c r="C51">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>16.780941900690987</v>
       </c>
@@ -1828,7 +2336,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>15.353540775918445</v>
       </c>
@@ -1839,7 +2347,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>13.924797128343462</v>
       </c>
@@ -1850,7 +2358,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>12.494955104232433</v>
       </c>
@@ -1861,7 +2369,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>11.063952340570562</v>
       </c>
@@ -1872,9 +2380,9 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>9.6316498470227288</v>
+        <v>9.6316498470227287</v>
       </c>
       <c r="B57">
         <v>-5.2871268845821637</v>
@@ -1883,9 +2391,9 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>8.19790863325383</v>
+        <v>8.1979086332538298</v>
       </c>
       <c r="B58">
         <v>-4.6213220336233185</v>
@@ -1894,7 +2402,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>6.7626064353562274</v>
       </c>
@@ -1905,7 +2413,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>5.3256878951321793</v>
       </c>
@@ -1916,7 +2424,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>3.8871143808114352</v>
       </c>
@@ -1927,18 +2435,18 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2.4468472606237213</v>
       </c>
       <c r="B62">
-        <v>-1.99275710423359</v>
+        <v>-1.9927571042335901</v>
       </c>
       <c r="C62">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>1.0049503234542336</v>
       </c>
@@ -1949,9 +2457,9 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>-0.438102959190075</v>
+        <v>-0.43810295919007503</v>
       </c>
       <c r="B64">
         <v>-0.69875411811643617</v>
@@ -1960,18 +2468,18 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>-1.881736695146794</v>
       </c>
       <c r="B65">
-        <v>-0.054247051364641162</v>
+        <v>-5.4247051364641162E-2</v>
       </c>
       <c r="C65">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>-3.3253749922535172</v>
       </c>
@@ -1982,7 +2490,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>-4.7691863762559983</v>
       </c>
@@ -1993,7 +2501,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>-6.2163170445326408</v>
       </c>
@@ -2004,7 +2512,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>-7.6692040323508355</v>
       </c>
@@ -2015,7 +2523,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>-9.1244700549012538</v>
       </c>
@@ -2026,7 +2534,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>-10.578432925803886</v>
       </c>
@@ -2037,7 +2545,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>-12.03200517247269</v>
       </c>
@@ -2048,9 +2556,9 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>-13.486710732321289</v>
+        <v>-13.486710732321288</v>
       </c>
       <c r="B73">
         <v>4.9814524604296615</v>
@@ -2059,7 +2567,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>-14.941924468967946</v>
       </c>
@@ -2070,7 +2578,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>-16.396472259524266</v>
       </c>
@@ -2081,7 +2589,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>-17.849133108870522</v>
       </c>
@@ -2092,7 +2600,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>-19.298776677311043</v>
       </c>
@@ -2103,7 +2611,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>-20.744682119077602</v>
       </c>
@@ -2114,7 +2622,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>-22.185619974609747</v>
       </c>
@@ -2125,7 +2633,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>-23.619432605226049</v>
       </c>
@@ -2136,18 +2644,18 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>-25.04081973364465</v>
       </c>
       <c r="B81">
-        <v>10.126660198404681</v>
+        <v>10.12666019840468</v>
       </c>
       <c r="C81">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>-26.354322818002842</v>
       </c>
@@ -2164,13 +2672,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C82"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>-33.7845194164989</v>
+        <v>-33.784519416498902</v>
       </c>
       <c r="B1">
         <v>10.218576630129853</v>
@@ -2179,18 +2687,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>-32.063549491257646</v>
       </c>
       <c r="B2">
-        <v>9.80808900924465</v>
+        <v>9.8080890092446502</v>
       </c>
       <c r="C2">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>-30.345550375447761</v>
       </c>
@@ -2201,18 +2709,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>-28.62968768276038</v>
       </c>
       <c r="B4">
-        <v>8.96155399297963</v>
+        <v>8.9615539929796295</v>
       </c>
       <c r="C4">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>-26.915127026886623</v>
       </c>
@@ -2223,7 +2731,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>-25.20138963611215</v>
       </c>
@@ -2234,7 +2742,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>-23.489419197100759</v>
       </c>
@@ -2245,7 +2753,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>-21.780209326937644</v>
       </c>
@@ -2256,7 +2764,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>-20.073530906015304</v>
       </c>
@@ -2267,7 +2775,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>-18.368935367716432</v>
       </c>
@@ -2278,7 +2786,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>-16.666319094077128</v>
       </c>
@@ -2289,7 +2797,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>-14.965664704296822</v>
       </c>
@@ -2300,7 +2808,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>-13.266954817574963</v>
       </c>
@@ -2311,7 +2819,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>-11.570170891640736</v>
       </c>
@@ -2322,7 +2830,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>-9.8752897383423122</v>
       </c>
@@ -2333,18 +2841,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>-8.1822870080576138</v>
       </c>
       <c r="B16">
-        <v>3.38947067363685</v>
+        <v>3.3894706736368501</v>
       </c>
       <c r="C16">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>-6.4911383511645555</v>
       </c>
@@ -2355,7 +2863,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>-4.8018292542807952</v>
       </c>
@@ -2366,7 +2874,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>-3.1143845489829673</v>
       </c>
@@ -2377,7 +2885,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>-1.4288389030874458</v>
       </c>
@@ -2388,7 +2896,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>0.25477301558939996</v>
       </c>
@@ -2399,7 +2907,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1.9364280951699884</v>
       </c>
@@ -2410,7 +2918,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>3.6161494475319076</v>
       </c>
@@ -2421,7 +2929,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>5.293971740491517</v>
       </c>
@@ -2432,7 +2940,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>6.9699296418652006</v>
       </c>
@@ -2443,18 +2951,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>8.64404798322957</v>
+        <v>8.6440479832295694</v>
       </c>
       <c r="B26">
-        <v>-1.92841037989777</v>
+        <v>-1.9284103798977701</v>
       </c>
       <c r="C26">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>10.316312251202312</v>
       </c>
@@ -2465,7 +2973,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>11.986698096161325</v>
       </c>
@@ -2476,7 +2984,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>13.655181168484539</v>
       </c>
@@ -2487,7 +2995,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>15.321738280020115</v>
       </c>
@@ -2498,7 +3006,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>16.986350888497249</v>
       </c>
@@ -2509,7 +3017,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>18.649001613115377</v>
       </c>
@@ -2520,7 +3028,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>20.309673073073942</v>
       </c>
@@ -2531,18 +3039,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>21.96826165040904</v>
       </c>
       <c r="B34">
-        <v>-6.61573670413545</v>
+        <v>-6.6157367041354496</v>
       </c>
       <c r="C34">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>23.624318778503362</v>
       </c>
@@ -2553,7 +3061,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>25.277615337749413</v>
       </c>
@@ -2564,18 +3072,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>26.92914494523238</v>
       </c>
       <c r="B37">
-        <v>-8.48643260162591</v>
+        <v>-8.4864326016259106</v>
       </c>
       <c r="C37">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>28.579851287616055</v>
       </c>
@@ -2586,7 +3094,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>30.229255593186107</v>
       </c>
@@ -2597,7 +3105,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>31.876523475633668</v>
       </c>
@@ -2608,7 +3116,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>33.520820548649837</v>
       </c>
@@ -2619,7 +3127,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>33.482531805064383</v>
       </c>
@@ -2630,18 +3138,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>31.799218126460723</v>
       </c>
       <c r="B43">
-        <v>-10.64446124999288</v>
+        <v>-10.644461249992879</v>
       </c>
       <c r="C43">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>30.116941945335459</v>
       </c>
@@ -2652,18 +3160,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>28.434869208751255</v>
       </c>
       <c r="B45">
-        <v>-9.57798013586792</v>
+        <v>-9.5779801358679197</v>
       </c>
       <c r="C45">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>26.752165863770749</v>
       </c>
@@ -2674,7 +3182,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>25.068353463518633</v>
       </c>
@@ -2685,7 +3193,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>23.384375985367875</v>
       </c>
@@ -2696,7 +3204,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>21.701227324342735</v>
       </c>
@@ -2707,7 +3215,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>20.018678621824527</v>
       </c>
@@ -2718,7 +3226,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>18.336281557280227</v>
       </c>
@@ -2729,18 +3237,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>16.653932716162338</v>
       </c>
       <c r="B52">
-        <v>-5.86337998540387</v>
+        <v>-5.8633799854038697</v>
       </c>
       <c r="C52">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>14.971614910419747</v>
       </c>
@@ -2751,7 +3259,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>13.289310952001358</v>
       </c>
@@ -2762,7 +3270,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>11.607002478238378</v>
       </c>
@@ -2773,7 +3281,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>9.9246664279913563</v>
       </c>
@@ -2784,9 +3292,9 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>8.24227856550314</v>
+        <v>8.2422785655031401</v>
       </c>
       <c r="B57">
         <v>-3.1996510759313788</v>
@@ -2795,7 +3303,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>6.559814655016611</v>
       </c>
@@ -2806,7 +3314,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>4.8772602844208857</v>
       </c>
@@ -2817,7 +3325,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>3.1946403361902727</v>
       </c>
@@ -2828,18 +3336,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>1.5119895164453261</v>
       </c>
       <c r="B61">
-        <v>-1.071723614999673</v>
+        <v>-1.0717236149996729</v>
       </c>
       <c r="C61">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>-0.1706574686933697</v>
       </c>
@@ -2850,18 +3358,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>-1.8532774818121083</v>
       </c>
       <c r="B63">
-        <v>-0.0081474042927496843</v>
+        <v>-8.1474042927496843E-3</v>
       </c>
       <c r="C63">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>-3.5358936603246023</v>
       </c>
@@ -2872,7 +3380,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>-5.2185407103514256</v>
       </c>
@@ -2883,7 +3391,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>-6.9012533380131451</v>
       </c>
@@ -2894,7 +3402,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>-8.584056425784043</v>
       </c>
@@ -2905,7 +3413,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>-10.266935561553266</v>
       </c>
@@ -2916,7 +3424,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>-11.949866509563682</v>
       </c>
@@ -2927,7 +3435,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>-13.632825034058143</v>
       </c>
@@ -2938,7 +3446,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>-15.31578807389719</v>
       </c>
@@ -2949,7 +3457,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>-16.998737266412039</v>
       </c>
@@ -2960,7 +3468,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>-18.681655423551582</v>
       </c>
@@ -2971,7 +3479,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>-20.364525357264718</v>
       </c>
@@ -2982,7 +3490,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>-22.04724365300395</v>
       </c>
@@ -2993,18 +3501,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>-23.729361990236246</v>
       </c>
       <c r="B76">
-        <v>6.89924747232974</v>
+        <v>6.8992474723297397</v>
       </c>
       <c r="C76">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>-25.410651510342927</v>
       </c>
@@ -3015,7 +3523,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>-27.092106108348254</v>
       </c>
@@ -3026,7 +3534,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>-28.774669761625184</v>
       </c>
@@ -3037,7 +3545,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>-30.457864023298413</v>
       </c>
@@ -3048,9 +3556,9 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>-32.1408548404306</v>
+        <v>-32.140854840430599</v>
       </c>
       <c r="B81">
         <v>9.5634867534386814</v>
@@ -3059,7 +3567,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>-33.822808160084357</v>
       </c>

--- a/src/nodes/HPC/compressor_stage_1_blade_rotor_coordinates_lattice.xlsx
+++ b/src/nodes/HPC/compressor_stage_1_blade_rotor_coordinates_lattice.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\projects\gte\src\nodes\HPC\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="600" yWindow="216" windowWidth="15132" windowHeight="6720"/>
+    <workbookView xWindow="600" yWindow="210" windowWidth="15135" windowHeight="6720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,497 +15,9 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="161">
-  <si>
-    <t>-19.2149570359165</t>
-  </si>
-  <si>
-    <t>15.5473448514592</t>
-  </si>
-  <si>
-    <t>182.168420475777</t>
-  </si>
-  <si>
-    <t>-17.1728776902364</t>
-  </si>
-  <si>
-    <t>15.62580959791</t>
-  </si>
-  <si>
-    <t>-15.6514512899292</t>
-  </si>
-  <si>
-    <t>15.2045551447825</t>
-  </si>
-  <si>
-    <t>-14.2161177720786</t>
-  </si>
-  <si>
-    <t>14.7006693213862</t>
-  </si>
-  <si>
-    <t>-12.8425575466197</t>
-  </si>
-  <si>
-    <t>14.1374939069031</t>
-  </si>
-  <si>
-    <t>-11.5207644108359</t>
-  </si>
-  <si>
-    <t>13.5246327874858</t>
-  </si>
-  <si>
-    <t>-10.2449729623491</t>
-  </si>
-  <si>
-    <t>12.8676195576088</t>
-  </si>
-  <si>
-    <t>-9.01174048975304</t>
-  </si>
-  <si>
-    <t>12.1697585085539</t>
-  </si>
-  <si>
-    <t>-7.81577926754523</t>
-  </si>
-  <si>
-    <t>11.4361247637391</t>
-  </si>
-  <si>
-    <t>-6.65139768148118</t>
-  </si>
-  <si>
-    <t>10.6721810962839</t>
-  </si>
-  <si>
-    <t>-5.51313357644527</t>
-  </si>
-  <si>
-    <t>9.88317004597735</t>
-  </si>
-  <si>
-    <t>-4.39803053364503</t>
-  </si>
-  <si>
-    <t>9.07192916371714</t>
-  </si>
-  <si>
-    <t>-3.31292562045161</t>
-  </si>
-  <si>
-    <t>8.23189627816724</t>
-  </si>
-  <si>
-    <t>-2.26188159697026</t>
-  </si>
-  <si>
-    <t>7.35917197946946</t>
-  </si>
-  <si>
-    <t>-1.22807050807894</t>
-  </si>
-  <si>
-    <t>6.46990762591125</t>
-  </si>
-  <si>
-    <t>-0.196058175172618</t>
-  </si>
-  <si>
-    <t>5.57891683844145</t>
-  </si>
-  <si>
-    <t>0.823123759058402</t>
-  </si>
-  <si>
-    <t>4.67561152050893</t>
-  </si>
-  <si>
-    <t>1.81520875687362</t>
-  </si>
-  <si>
-    <t>3.74629874502322</t>
-  </si>
-  <si>
-    <t>2.77945652162714</t>
-  </si>
-  <si>
-    <t>2.7902679802364</t>
-  </si>
-  <si>
-    <t>3.7185083169467</t>
-  </si>
-  <si>
-    <t>1.81005429323615</t>
-  </si>
-  <si>
-    <t>4.63500540646004</t>
-  </si>
-  <si>
-    <t>0.808192751110197</t>
-  </si>
-  <si>
-    <t>5.53111619648142</t>
-  </si>
-  <si>
-    <t>-0.213235424326927</t>
-  </si>
-  <si>
-    <t>6.40711766407109</t>
-  </si>
-  <si>
-    <t>-1.25396439235334</t>
-  </si>
-  <si>
-    <t>7.26281392897579</t>
-  </si>
-  <si>
-    <t>-2.3141821575203</t>
-  </si>
-  <si>
-    <t>8.09800911094228</t>
-  </si>
-  <si>
-    <t>-3.39407672437909</t>
-  </si>
-  <si>
-    <t>8.91242449924425</t>
-  </si>
-  <si>
-    <t>-4.49391559761266</t>
-  </si>
-  <si>
-    <t>9.70545006126305</t>
-  </si>
-  <si>
-    <t>-5.61428428243058</t>
-  </si>
-  <si>
-    <t>10.476392933907</t>
-  </si>
-  <si>
-    <t>-6.75584778417407</t>
-  </si>
-  <si>
-    <t>11.2245602540844</t>
-  </si>
-  <si>
-    <t>-7.9192711081844</t>
-  </si>
-  <si>
-    <t>11.9496006071157</t>
-  </si>
-  <si>
-    <t>-9.10489153991034</t>
-  </si>
-  <si>
-    <t>12.6525283719704</t>
-  </si>
-  <si>
-    <t>-10.3117354852309</t>
-  </si>
-  <si>
-    <t>13.3346993760303</t>
-  </si>
-  <si>
-    <t>-11.5385016301327</t>
-  </si>
-  <si>
-    <t>13.9974694466769</t>
-  </si>
-  <si>
-    <t>-12.7838886606023</t>
-  </si>
-  <si>
-    <t>14.6416248496004</t>
-  </si>
-  <si>
-    <t>-14.047141924112</t>
-  </si>
-  <si>
-    <t>15.2656736037245</t>
-  </si>
-  <si>
-    <t>-15.3296934140766</t>
-  </si>
-  <si>
-    <t>15.8675541662813</t>
-  </si>
-  <si>
-    <t>-16.6335217853967</t>
-  </si>
-  <si>
-    <t>16.4452049945029</t>
-  </si>
-  <si>
-    <t>-17.960605692973</t>
-  </si>
-  <si>
-    <t>16.9951783752931</t>
-  </si>
-  <si>
-    <t>-19.3142542286757</t>
-  </si>
-  <si>
-    <t>17.5084819142428</t>
-  </si>
-  <si>
-    <t>-20.703098232254</t>
-  </si>
-  <si>
-    <t>17.9747370466145</t>
-  </si>
-  <si>
-    <t>-22.1370989804269</t>
-  </si>
-  <si>
-    <t>18.3835652076706</t>
-  </si>
-  <si>
-    <t>-23.6262177499133</t>
-  </si>
-  <si>
-    <t>17.4933387376264</t>
-  </si>
-  <si>
-    <t>-22.599141843689</t>
-  </si>
-  <si>
-    <t>16.6283616485653</t>
-  </si>
-  <si>
-    <t>-21.5478317512051</t>
-  </si>
-  <si>
-    <t>15.7786377868873</t>
-  </si>
-  <si>
-    <t>-20.4818817135396</t>
-  </si>
-  <si>
-    <t>14.9341709989926</t>
-  </si>
-  <si>
-    <t>-19.4108859717704</t>
-  </si>
-  <si>
-    <t>14.0863350952963</t>
-  </si>
-  <si>
-    <t>-18.3431238847162</t>
-  </si>
-  <si>
-    <t>13.231983742273</t>
-  </si>
-  <si>
-    <t>-17.2816152821596</t>
-  </si>
-  <si>
-    <t>12.3693405704128</t>
-  </si>
-  <si>
-    <t>-16.228065111624</t>
-  </si>
-  <si>
-    <t>11.4966292102053</t>
-  </si>
-  <si>
-    <t>-15.1841783206329</t>
-  </si>
-  <si>
-    <t>10.6126271890528</t>
-  </si>
-  <si>
-    <t>-14.1511282301739</t>
-  </si>
-  <si>
-    <t>9.71832762200719</t>
-  </si>
-  <si>
-    <t>-13.1279616550911</t>
-  </si>
-  <si>
-    <t>8.81527752103286</t>
-  </si>
-  <si>
-    <t>-12.1131937836931</t>
-  </si>
-  <si>
-    <t>7.90502389809414</t>
-  </si>
-  <si>
-    <t>-11.1053398042882</t>
-  </si>
-  <si>
-    <t>6.9887589818315</t>
-  </si>
-  <si>
-    <t>-10.1032554238358</t>
-  </si>
-  <si>
-    <t>6.06625586759006</t>
-  </si>
-  <si>
-    <t>-9.10715842389948</t>
-  </si>
-  <si>
-    <t>5.13693286739102</t>
-  </si>
-  <si>
-    <t>-8.11760710469394</t>
-  </si>
-  <si>
-    <t>4.20020829325564</t>
-  </si>
-  <si>
-    <t>-7.13515976643381</t>
-  </si>
-  <si>
-    <t>3.25557091291224</t>
-  </si>
-  <si>
-    <t>-6.16030708641931</t>
-  </si>
-  <si>
-    <t>2.30279131691746</t>
-  </si>
-  <si>
-    <t>-5.19326925029315</t>
-  </si>
-  <si>
-    <t>1.34171055153506</t>
-  </si>
-  <si>
-    <t>-4.23419882078366</t>
-  </si>
-  <si>
-    <t>0.37216966302877</t>
-  </si>
-  <si>
-    <t>-3.28324836061916</t>
-  </si>
-  <si>
-    <t>-0.605530006327272</t>
-  </si>
-  <si>
-    <t>-2.34012864350914</t>
-  </si>
-  <si>
-    <t>-1.58924593021737</t>
-  </si>
-  <si>
-    <t>-1.40278328708781</t>
-  </si>
-  <si>
-    <t>-2.57637528631541</t>
-  </si>
-  <si>
-    <t>-0.468714119970579</t>
-  </si>
-  <si>
-    <t>-3.56431525229532</t>
-  </si>
-  <si>
-    <t>0.464577029227174</t>
-  </si>
-  <si>
-    <t>-4.55385482776736</t>
-  </si>
-  <si>
-    <t>1.39633288397946</t>
-  </si>
-  <si>
-    <t>-5.55935030008733</t>
-  </si>
-  <si>
-    <t>2.3127743761179</t>
-  </si>
-  <si>
-    <t>-6.59193810977239</t>
-  </si>
-  <si>
-    <t>3.20321282484113</t>
-  </si>
-  <si>
-    <t>-7.63630802223957</t>
-  </si>
-  <si>
-    <t>4.08234289045819</t>
-  </si>
-  <si>
-    <t>-8.67576796308454</t>
-  </si>
-  <si>
-    <t>4.96618551385642</t>
-  </si>
-  <si>
-    <t>-9.71454517371759</t>
-  </si>
-  <si>
-    <t>5.85068341712594</t>
-  </si>
-  <si>
-    <t>-10.7596553597618</t>
-  </si>
-  <si>
-    <t>6.72910297313638</t>
-  </si>
-  <si>
-    <t>-11.8083487678771</t>
-  </si>
-  <si>
-    <t>7.60408337667269</t>
-  </si>
-  <si>
-    <t>-12.8553844602072</t>
-  </si>
-  <si>
-    <t>8.48065484468419</t>
-  </si>
-  <si>
-    <t>-13.8953222197954</t>
-  </si>
-  <si>
-    <t>9.36403886086239</t>
-  </si>
-  <si>
-    <t>-14.9231417918853</t>
-  </si>
-  <si>
-    <t>10.2590538319996</t>
-  </si>
-  <si>
-    <t>-15.9357020496241</t>
-  </si>
-  <si>
-    <t>11.1687145905495</t>
-  </si>
-  <si>
-    <t>-16.9275550810952</t>
-  </si>
-  <si>
-    <t>12.0982500057741</t>
-  </si>
-  <si>
-    <t>-17.8890451857196</t>
-  </si>
-  <si>
-    <t>13.0569275542288</t>
-  </si>
-  <si>
-    <t>-18.7962301244373</t>
-  </si>
-  <si>
-    <t>14.0677268361357</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -538,30 +45,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -599,9 +97,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -633,10 +131,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -668,10 +165,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -844,927 +340,923 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C82"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>2</v>
+    <row r="1" spans="1:3">
+      <c r="A1">
+        <v>-19.214957035916488</v>
+      </c>
+      <c r="B1">
+        <v>15.547344851459163</v>
+      </c>
+      <c r="C1">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>-17.172877690236444</v>
+      </c>
+      <c r="B2">
+        <v>15.625809597909973</v>
+      </c>
+      <c r="C2">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>-15.651451289929165</v>
+      </c>
+      <c r="B3">
+        <v>15.204555144782525</v>
+      </c>
+      <c r="C3">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>-14.216117772078622</v>
+      </c>
+      <c r="B4">
+        <v>14.700669321386213</v>
+      </c>
+      <c r="C4">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>-12.842557546619741</v>
+      </c>
+      <c r="B5">
+        <v>14.137493906903135</v>
+      </c>
+      <c r="C5">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>-11.520764410835929</v>
+      </c>
+      <c r="B6">
+        <v>13.524632787485837</v>
+      </c>
+      <c r="C6">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>-10.244972962349072</v>
+      </c>
+      <c r="B7">
+        <v>12.867619557608808</v>
+      </c>
+      <c r="C7">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>-9.011740489753036</v>
+      </c>
+      <c r="B8">
+        <v>12.169758508553871</v>
+      </c>
+      <c r="C8">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>-7.8157792675452313</v>
+      </c>
+      <c r="B9">
+        <v>11.436124763739082</v>
+      </c>
+      <c r="C9">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>-6.6513976814811757</v>
+      </c>
+      <c r="B10">
+        <v>10.672181096283932</v>
+      </c>
+      <c r="C10">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>-5.5131335764452682</v>
+      </c>
+      <c r="B11">
+        <v>9.8831700459773462</v>
+      </c>
+      <c r="C11">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>-4.3980305336450281</v>
+      </c>
+      <c r="B12">
+        <v>9.0719291637171438</v>
+      </c>
+      <c r="C12">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>-3.3129256204516113</v>
+      </c>
+      <c r="B13">
+        <v>8.2318962781672358</v>
+      </c>
+      <c r="C13">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>-2.2618815969702633</v>
+      </c>
+      <c r="B14">
+        <v>7.3591719794694583</v>
+      </c>
+      <c r="C14">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>-1.2280705080789405</v>
+      </c>
+      <c r="B15">
+        <v>6.4699076259112456</v>
+      </c>
+      <c r="C15">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>-0.19605817517261842</v>
+      </c>
+      <c r="B16">
+        <v>5.5789168384414465</v>
+      </c>
+      <c r="C16">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>0.82312375905840229</v>
+      </c>
+      <c r="B17">
+        <v>4.6756115205089293</v>
+      </c>
+      <c r="C17">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>1.8152087568736208</v>
+      </c>
+      <c r="B18">
+        <v>3.7462987450232221</v>
+      </c>
+      <c r="C18">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>2.7794565216271363</v>
+      </c>
+      <c r="B19">
+        <v>2.7902679802363966</v>
+      </c>
+      <c r="C19">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>3.7185083169466986</v>
+      </c>
+      <c r="B20">
+        <v>1.8100542932361496</v>
+      </c>
+      <c r="C20">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>4.6350054064600439</v>
+      </c>
+      <c r="B21">
+        <v>0.80819275111019739</v>
+      </c>
+      <c r="C21">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>5.5311161964814222</v>
+      </c>
+      <c r="B22">
+        <v>-0.21323542432692688</v>
+      </c>
+      <c r="C22">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>6.4071176640710883</v>
+      </c>
+      <c r="B23">
+        <v>-1.253964392353335</v>
+      </c>
+      <c r="C23">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>7.2628139289757909</v>
+      </c>
+      <c r="B24">
+        <v>-2.3141821575202974</v>
+      </c>
+      <c r="C24">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>8.098009110942284</v>
+      </c>
+      <c r="B25">
+        <v>-3.3940767243790941</v>
+      </c>
+      <c r="C25">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>8.9124244992442474</v>
+      </c>
+      <c r="B26">
+        <v>-4.4939155976126566</v>
+      </c>
+      <c r="C26">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>9.7054500612630523</v>
+      </c>
+      <c r="B27">
+        <v>-5.6142842824305754</v>
+      </c>
+      <c r="C27">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>10.476392933906991</v>
+      </c>
+      <c r="B28">
+        <v>-6.7558477841740716</v>
+      </c>
+      <c r="C28">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>11.224560254084363</v>
+      </c>
+      <c r="B29">
+        <v>-7.9192711081843994</v>
+      </c>
+      <c r="C29">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>11.94960060711569</v>
+      </c>
+      <c r="B30">
+        <v>-9.1048915399103389</v>
+      </c>
+      <c r="C30">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>12.65252837197043</v>
+      </c>
+      <c r="B31">
+        <v>-10.311735485230916</v>
+      </c>
+      <c r="C31">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>13.334699376030272</v>
+      </c>
+      <c r="B32">
+        <v>-11.538501630132718</v>
+      </c>
+      <c r="C32">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>13.9974694466769</v>
+      </c>
+      <c r="B33">
+        <v>-12.783888660602317</v>
+      </c>
+      <c r="C33">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>14.641624849600401</v>
+      </c>
+      <c r="B34">
+        <v>-14.047141924111953</v>
+      </c>
+      <c r="C34">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>15.26567360372449</v>
+      </c>
+      <c r="B35">
+        <v>-15.329693414076557</v>
+      </c>
+      <c r="C35">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>15.867554166281275</v>
+      </c>
+      <c r="B36">
+        <v>-16.633521785396695</v>
+      </c>
+      <c r="C36">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>16.445204994502863</v>
+      </c>
+      <c r="B37">
+        <v>-17.960605692972962</v>
+      </c>
+      <c r="C37">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>16.995178375293115</v>
+      </c>
+      <c r="B38">
+        <v>-19.314254228675672</v>
+      </c>
+      <c r="C38">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>17.508481914242811</v>
+      </c>
+      <c r="B39">
+        <v>-20.703098232254018</v>
+      </c>
+      <c r="C39">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>17.974737046614468</v>
+      </c>
+      <c r="B40">
+        <v>-22.137098980426931</v>
+      </c>
+      <c r="C40">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>18.383565207670614</v>
+      </c>
+      <c r="B41">
+        <v>-23.626217749913337</v>
+      </c>
+      <c r="C41">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>18.383565207670614</v>
+      </c>
+      <c r="B42">
+        <v>-23.626217749913337</v>
+      </c>
+      <c r="C42">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>17.493338737626377</v>
+      </c>
+      <c r="B43">
+        <v>-22.599141843688994</v>
+      </c>
+      <c r="C43">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>16.628361648565257</v>
+      </c>
+      <c r="B44">
+        <v>-21.547831751205138</v>
+      </c>
+      <c r="C44">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>15.778637786887318</v>
+      </c>
+      <c r="B45">
+        <v>-20.481881713539643</v>
+      </c>
+      <c r="C45">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>14.934170998992643</v>
+      </c>
+      <c r="B46">
+        <v>-19.410885971770394</v>
+      </c>
+      <c r="C46">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>14.086335095296272</v>
+      </c>
+      <c r="B47">
+        <v>-18.343123884716217</v>
+      </c>
+      <c r="C47">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>13.231983742273048</v>
+      </c>
+      <c r="B48">
+        <v>-17.281615282159617</v>
+      </c>
+      <c r="C48">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>12.36934057041278</v>
+      </c>
+      <c r="B49">
+        <v>-16.22806511162403</v>
+      </c>
+      <c r="C49">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>11.496629210205281</v>
+      </c>
+      <c r="B50">
+        <v>-15.184178320632919</v>
+      </c>
+      <c r="C50">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>10.612627189052775</v>
+      </c>
+      <c r="B51">
+        <v>-14.151128230173875</v>
+      </c>
+      <c r="C51">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>9.7183276220071875</v>
+      </c>
+      <c r="B52">
+        <v>-13.127961655091138</v>
+      </c>
+      <c r="C52">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>8.8152775210328613</v>
+      </c>
+      <c r="B53">
+        <v>-12.113193783693109</v>
+      </c>
+      <c r="C53">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>7.9050238980941394</v>
+      </c>
+      <c r="B54">
+        <v>-11.105339804288175</v>
+      </c>
+      <c r="C54">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>6.9887589818315048</v>
+      </c>
+      <c r="B55">
+        <v>-10.103255423835762</v>
+      </c>
+      <c r="C55">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>6.0662558675900558</v>
+      </c>
+      <c r="B56">
+        <v>-9.1071584238994774</v>
+      </c>
+      <c r="C56">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
+        <v>5.1369328673910184</v>
+      </c>
+      <c r="B57">
+        <v>-8.117607104693942</v>
+      </c>
+      <c r="C57">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58">
+        <v>4.200208293255641</v>
+      </c>
+      <c r="B58">
+        <v>-7.1351597664338051</v>
+      </c>
+      <c r="C58">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
+        <v>3.2555709129122365</v>
+      </c>
+      <c r="B59">
+        <v>-6.160307086419305</v>
+      </c>
+      <c r="C59">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
+        <v>2.3027913169174634</v>
+      </c>
+      <c r="B60">
+        <v>-5.1932692502931515</v>
+      </c>
+      <c r="C60">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
+        <v>1.3417105515350594</v>
+      </c>
+      <c r="B61">
+        <v>-4.23419882078366</v>
+      </c>
+      <c r="C61">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62">
+        <v>0.37216966302877</v>
+      </c>
+      <c r="B62">
+        <v>-3.2832483606191554</v>
+      </c>
+      <c r="C62">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>-0.60553000632727161</v>
+      </c>
+      <c r="B63">
+        <v>-2.3401286435091371</v>
+      </c>
+      <c r="C63">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>-1.5892459302173689</v>
+      </c>
+      <c r="B64">
+        <v>-1.4027832870878105</v>
+      </c>
+      <c r="C64">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <v>-2.5763752863154141</v>
+      </c>
+      <c r="B65">
+        <v>-0.46871411997057866</v>
+      </c>
+      <c r="C65">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
+        <v>-3.5643152522953176</v>
+      </c>
+      <c r="B66">
+        <v>0.4645770292271737</v>
+      </c>
+      <c r="C66">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
+        <v>-4.55385482776736</v>
+      </c>
+      <c r="B67">
+        <v>1.3963328839794584</v>
+      </c>
+      <c r="C67">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68">
+        <v>-5.5593503000873321</v>
+      </c>
+      <c r="B68">
+        <v>2.3127743761178965</v>
+      </c>
+      <c r="C68">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
+        <v>-6.5919381097723884</v>
+      </c>
+      <c r="B69">
+        <v>3.2032128248411307</v>
+      </c>
+      <c r="C69">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70">
+        <v>-7.6363080222395672</v>
+      </c>
+      <c r="B70">
+        <v>4.0823428904581949</v>
+      </c>
+      <c r="C70">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71">
+        <v>-8.675767963084537</v>
+      </c>
+      <c r="B71">
+        <v>4.9661855138564235</v>
+      </c>
+      <c r="C71">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72">
+        <v>-9.714545173717589</v>
+      </c>
+      <c r="B72">
+        <v>5.8506834171259374</v>
+      </c>
+      <c r="C72">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73">
+        <v>-10.759655359761842</v>
+      </c>
+      <c r="B73">
+        <v>6.729102973136377</v>
+      </c>
+      <c r="C73">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74">
+        <v>-11.808348767877115</v>
+      </c>
+      <c r="B74">
+        <v>7.6040833766726852</v>
+      </c>
+      <c r="C74">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75">
+        <v>-12.855384460207237</v>
+      </c>
+      <c r="B75">
+        <v>8.480654844684187</v>
+      </c>
+      <c r="C75">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76">
+        <v>-13.895322219795366</v>
+      </c>
+      <c r="B76">
+        <v>9.3640388608623866</v>
+      </c>
+      <c r="C76">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77">
+        <v>-14.923141791885314</v>
+      </c>
+      <c r="B77">
+        <v>10.259053831999648</v>
+      </c>
+      <c r="C77">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78">
+        <v>-15.935702049624114</v>
+      </c>
+      <c r="B78">
+        <v>11.1687145905495</v>
+      </c>
+      <c r="C78">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79">
+        <v>-16.927555081095221</v>
+      </c>
+      <c r="B79">
+        <v>12.098250005774091</v>
+      </c>
+      <c r="C79">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80">
+        <v>-17.88904518571956</v>
+      </c>
+      <c r="B80">
+        <v>13.05692755422883</v>
+      </c>
+      <c r="C80">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81">
+        <v>-18.796230124437319</v>
+      </c>
+      <c r="B81">
+        <v>14.067726836135725</v>
+      </c>
+      <c r="C81">
+        <v>182.16842047577737</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82">
+        <v>-19.214957035916488</v>
+      </c>
+      <c r="B82">
+        <v>15.547344851459163</v>
+      </c>
+      <c r="C82">
+        <v>182.16842047577737</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C82"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1">
         <v>-26.354322818002842</v>
       </c>
@@ -1775,7 +1267,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>-24.6840429746773</v>
       </c>
@@ -1786,7 +1278,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>-23.127659234757541</v>
       </c>
@@ -1797,7 +1289,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>-21.589706360983204</v>
       </c>
@@ -1808,7 +1300,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>-20.064877754018198</v>
       </c>
@@ -1819,7 +1311,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>-18.551009803513136</v>
       </c>
@@ -1830,7 +1322,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>-17.046867531949353</v>
       </c>
@@ -1841,18 +1333,18 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>-15.551724803881276</v>
       </c>
       <c r="B8">
-        <v>8.0407103347870699</v>
+        <v>8.04071033478707</v>
       </c>
       <c r="C8">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>-14.064446494210413</v>
       </c>
@@ -1863,7 +1355,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>-12.583807069148953</v>
       </c>
@@ -1874,7 +1366,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>-11.108628349804764</v>
       </c>
@@ -1885,7 +1377,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>-9.6382813828396241</v>
       </c>
@@ -1896,9 +1388,9 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13">
-        <v>-8.1742867622352406</v>
+        <v>-8.17428676223524</v>
       </c>
       <c r="B13">
         <v>5.1610687985187216</v>
@@ -1907,7 +1399,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>-6.7175539185272859</v>
       </c>
@@ -1918,7 +1410,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>-5.2643980811473261</v>
       </c>
@@ -1929,7 +1421,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>-3.8114395966930816</v>
       </c>
@@ -1940,7 +1432,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>-2.3611134815309547</v>
       </c>
@@ -1951,7 +1443,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>-0.91656419861926164</v>
       </c>
@@ -1962,7 +1454,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>0.52204067248474584</v>
       </c>
@@ -1973,7 +1465,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>1.9552777730740831</v>
       </c>
@@ -1984,18 +1476,18 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>3.3837237444417627</v>
       </c>
       <c r="B21">
-        <v>2.4260679723415481E-2</v>
+        <v>0.024260679723415481</v>
       </c>
       <c r="C21">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22">
         <v>4.8078525621905506</v>
       </c>
@@ -2006,7 +1498,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23">
         <v>6.2277275391621627</v>
       </c>
@@ -2017,7 +1509,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24">
         <v>7.6433093225080784</v>
       </c>
@@ -2028,7 +1520,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25">
         <v>9.0545585593797551</v>
       </c>
@@ -2039,7 +1531,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26">
         <v>10.461418934463083</v>
       </c>
@@ -2050,7 +1542,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27">
         <v>11.863766282581617</v>
       </c>
@@ -2061,7 +1553,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28">
         <v>13.261459476093316</v>
       </c>
@@ -2072,7 +1564,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29">
         <v>14.654357387356152</v>
       </c>
@@ -2083,7 +1575,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30">
         <v>16.042395277658017</v>
       </c>
@@ -2094,7 +1586,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31">
         <v>17.425813964006544</v>
       </c>
@@ -2105,7 +1597,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32">
         <v>18.804930652339294</v>
       </c>
@@ -2116,7 +1608,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33">
         <v>20.180062548593828</v>
       </c>
@@ -2127,7 +1619,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34">
         <v>21.551403278971051</v>
       </c>
@@ -2138,9 +1630,9 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35">
-        <v>22.918652150725201</v>
+        <v>22.9186521507252</v>
       </c>
       <c r="B35">
         <v>-10.454089704676003</v>
@@ -2149,7 +1641,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36">
         <v>24.281384891373865</v>
       </c>
@@ -2160,7 +1652,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37">
         <v>25.639177228434637</v>
       </c>
@@ -2171,7 +1663,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38">
         <v>26.99130190906402</v>
       </c>
@@ -2182,18 +1674,18 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39">
-        <v>28.335819758974299</v>
+        <v>28.3358197589743</v>
       </c>
       <c r="B39">
-        <v>-13.801500364897048</v>
+        <v>-13.801500364897049</v>
       </c>
       <c r="C39">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40">
         <v>29.670488623516654</v>
       </c>
@@ -2204,29 +1696,29 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41">
         <v>30.993066348042294</v>
       </c>
       <c r="B41">
-        <v>-15.585730484066101</v>
+        <v>-15.5857304840661</v>
       </c>
       <c r="C41">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42">
         <v>30.993066348042294</v>
       </c>
       <c r="B42">
-        <v>-15.585730484066101</v>
+        <v>-15.5857304840661</v>
       </c>
       <c r="C42">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3">
       <c r="A43">
         <v>29.564687982303653</v>
       </c>
@@ -2237,7 +1729,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44">
         <v>28.14238889992335</v>
       </c>
@@ -2248,7 +1740,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3">
       <c r="A45">
         <v>26.723933345627387</v>
       </c>
@@ -2259,7 +1751,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3">
       <c r="A46">
         <v>25.307085564141786</v>
       </c>
@@ -2270,7 +1762,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3">
       <c r="A47">
         <v>23.889912556859091</v>
       </c>
@@ -2281,7 +1773,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3">
       <c r="A48">
         <v>22.471692351838044</v>
       </c>
@@ -2292,18 +1784,18 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3">
       <c r="A49">
         <v>21.052005733803913</v>
       </c>
       <c r="B49">
-        <v>-10.720294044477757</v>
+        <v>-10.720294044477758</v>
       </c>
       <c r="C49">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3">
       <c r="A50">
         <v>19.630433487481966</v>
       </c>
@@ -2314,18 +1806,18 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3">
       <c r="A51">
-        <v>18.206679729074398</v>
+        <v>18.2066797290744</v>
       </c>
       <c r="B51">
-        <v>-9.3409833920024603</v>
+        <v>-9.34098339200246</v>
       </c>
       <c r="C51">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3">
       <c r="A52">
         <v>16.780941900690987</v>
       </c>
@@ -2336,7 +1828,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3">
       <c r="A53">
         <v>15.353540775918445</v>
       </c>
@@ -2347,7 +1839,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3">
       <c r="A54">
         <v>13.924797128343462</v>
       </c>
@@ -2358,7 +1850,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3">
       <c r="A55">
         <v>12.494955104232433</v>
       </c>
@@ -2369,7 +1861,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3">
       <c r="A56">
         <v>11.063952340570562</v>
       </c>
@@ -2380,9 +1872,9 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3">
       <c r="A57">
-        <v>9.6316498470227287</v>
+        <v>9.6316498470227288</v>
       </c>
       <c r="B57">
         <v>-5.2871268845821637</v>
@@ -2391,9 +1883,9 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3">
       <c r="A58">
-        <v>8.1979086332538298</v>
+        <v>8.19790863325383</v>
       </c>
       <c r="B58">
         <v>-4.6213220336233185</v>
@@ -2402,7 +1894,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3">
       <c r="A59">
         <v>6.7626064353562274</v>
       </c>
@@ -2413,7 +1905,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3">
       <c r="A60">
         <v>5.3256878951321793</v>
       </c>
@@ -2424,7 +1916,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3">
       <c r="A61">
         <v>3.8871143808114352</v>
       </c>
@@ -2435,18 +1927,18 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3">
       <c r="A62">
         <v>2.4468472606237213</v>
       </c>
       <c r="B62">
-        <v>-1.9927571042335901</v>
+        <v>-1.99275710423359</v>
       </c>
       <c r="C62">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3">
       <c r="A63">
         <v>1.0049503234542336</v>
       </c>
@@ -2457,9 +1949,9 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.43810295919007503</v>
+        <v>-0.438102959190075</v>
       </c>
       <c r="B64">
         <v>-0.69875411811643617</v>
@@ -2468,18 +1960,18 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3">
       <c r="A65">
         <v>-1.881736695146794</v>
       </c>
       <c r="B65">
-        <v>-5.4247051364641162E-2</v>
+        <v>-0.054247051364641162</v>
       </c>
       <c r="C65">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3">
       <c r="A66">
         <v>-3.3253749922535172</v>
       </c>
@@ -2490,7 +1982,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3">
       <c r="A67">
         <v>-4.7691863762559983</v>
       </c>
@@ -2501,7 +1993,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3">
       <c r="A68">
         <v>-6.2163170445326408</v>
       </c>
@@ -2512,7 +2004,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3">
       <c r="A69">
         <v>-7.6692040323508355</v>
       </c>
@@ -2523,7 +2015,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3">
       <c r="A70">
         <v>-9.1244700549012538</v>
       </c>
@@ -2534,7 +2026,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3">
       <c r="A71">
         <v>-10.578432925803886</v>
       </c>
@@ -2545,7 +2037,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3">
       <c r="A72">
         <v>-12.03200517247269</v>
       </c>
@@ -2556,9 +2048,9 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3">
       <c r="A73">
-        <v>-13.486710732321288</v>
+        <v>-13.486710732321289</v>
       </c>
       <c r="B73">
         <v>4.9814524604296615</v>
@@ -2567,7 +2059,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3">
       <c r="A74">
         <v>-14.941924468967946</v>
       </c>
@@ -2578,7 +2070,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3">
       <c r="A75">
         <v>-16.396472259524266</v>
       </c>
@@ -2589,7 +2081,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3">
       <c r="A76">
         <v>-17.849133108870522</v>
       </c>
@@ -2600,7 +2092,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3">
       <c r="A77">
         <v>-19.298776677311043</v>
       </c>
@@ -2611,7 +2103,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3">
       <c r="A78">
         <v>-20.744682119077602</v>
       </c>
@@ -2622,7 +2114,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3">
       <c r="A79">
         <v>-22.185619974609747</v>
       </c>
@@ -2633,7 +2125,7 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3">
       <c r="A80">
         <v>-23.619432605226049</v>
       </c>
@@ -2644,18 +2136,18 @@
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3">
       <c r="A81">
         <v>-25.04081973364465</v>
       </c>
       <c r="B81">
-        <v>10.12666019840468</v>
+        <v>10.126660198404681</v>
       </c>
       <c r="C81">
         <v>230.80559063164714</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3">
       <c r="A82">
         <v>-26.354322818002842</v>
       </c>
@@ -2672,13 +2164,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C82"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1">
-        <v>-33.784519416498902</v>
+        <v>-33.7845194164989</v>
       </c>
       <c r="B1">
         <v>10.218576630129853</v>
@@ -2687,18 +2179,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>-32.063549491257646</v>
       </c>
       <c r="B2">
-        <v>9.8080890092446502</v>
+        <v>9.80808900924465</v>
       </c>
       <c r="C2">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>-30.345550375447761</v>
       </c>
@@ -2709,18 +2201,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>-28.62968768276038</v>
       </c>
       <c r="B4">
-        <v>8.9615539929796295</v>
+        <v>8.96155399297963</v>
       </c>
       <c r="C4">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>-26.915127026886623</v>
       </c>
@@ -2731,7 +2223,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>-25.20138963611215</v>
       </c>
@@ -2742,7 +2234,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>-23.489419197100759</v>
       </c>
@@ -2753,7 +2245,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>-21.780209326937644</v>
       </c>
@@ -2764,7 +2256,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>-20.073530906015304</v>
       </c>
@@ -2775,7 +2267,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>-18.368935367716432</v>
       </c>
@@ -2786,7 +2278,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>-16.666319094077128</v>
       </c>
@@ -2797,7 +2289,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>-14.965664704296822</v>
       </c>
@@ -2808,7 +2300,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>-13.266954817574963</v>
       </c>
@@ -2819,7 +2311,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>-11.570170891640736</v>
       </c>
@@ -2830,7 +2322,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>-9.8752897383423122</v>
       </c>
@@ -2841,18 +2333,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>-8.1822870080576138</v>
       </c>
       <c r="B16">
-        <v>3.3894706736368501</v>
+        <v>3.38947067363685</v>
       </c>
       <c r="C16">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>-6.4911383511645555</v>
       </c>
@@ -2863,7 +2355,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>-4.8018292542807952</v>
       </c>
@@ -2874,7 +2366,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>-3.1143845489829673</v>
       </c>
@@ -2885,7 +2377,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>-1.4288389030874458</v>
       </c>
@@ -2896,7 +2388,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>0.25477301558939996</v>
       </c>
@@ -2907,7 +2399,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22">
         <v>1.9364280951699884</v>
       </c>
@@ -2918,7 +2410,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23">
         <v>3.6161494475319076</v>
       </c>
@@ -2929,7 +2421,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24">
         <v>5.293971740491517</v>
       </c>
@@ -2940,7 +2432,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25">
         <v>6.9699296418652006</v>
       </c>
@@ -2951,18 +2443,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26">
-        <v>8.6440479832295694</v>
+        <v>8.64404798322957</v>
       </c>
       <c r="B26">
-        <v>-1.9284103798977701</v>
+        <v>-1.92841037989777</v>
       </c>
       <c r="C26">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27">
         <v>10.316312251202312</v>
       </c>
@@ -2973,7 +2465,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28">
         <v>11.986698096161325</v>
       </c>
@@ -2984,7 +2476,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29">
         <v>13.655181168484539</v>
       </c>
@@ -2995,7 +2487,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30">
         <v>15.321738280020115</v>
       </c>
@@ -3006,7 +2498,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31">
         <v>16.986350888497249</v>
       </c>
@@ -3017,7 +2509,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32">
         <v>18.649001613115377</v>
       </c>
@@ -3028,7 +2520,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33">
         <v>20.309673073073942</v>
       </c>
@@ -3039,18 +2531,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34">
         <v>21.96826165040904</v>
       </c>
       <c r="B34">
-        <v>-6.6157367041354496</v>
+        <v>-6.61573670413545</v>
       </c>
       <c r="C34">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35">
         <v>23.624318778503362</v>
       </c>
@@ -3061,7 +2553,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36">
         <v>25.277615337749413</v>
       </c>
@@ -3072,18 +2564,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37">
         <v>26.92914494523238</v>
       </c>
       <c r="B37">
-        <v>-8.4864326016259106</v>
+        <v>-8.48643260162591</v>
       </c>
       <c r="C37">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38">
         <v>28.579851287616055</v>
       </c>
@@ -3094,7 +2586,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39">
         <v>30.229255593186107</v>
       </c>
@@ -3105,7 +2597,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40">
         <v>31.876523475633668</v>
       </c>
@@ -3116,7 +2608,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41">
         <v>33.520820548649837</v>
       </c>
@@ -3127,7 +2619,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42">
         <v>33.482531805064383</v>
       </c>
@@ -3138,18 +2630,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3">
       <c r="A43">
         <v>31.799218126460723</v>
       </c>
       <c r="B43">
-        <v>-10.644461249992879</v>
+        <v>-10.64446124999288</v>
       </c>
       <c r="C43">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44">
         <v>30.116941945335459</v>
       </c>
@@ -3160,18 +2652,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3">
       <c r="A45">
         <v>28.434869208751255</v>
       </c>
       <c r="B45">
-        <v>-9.5779801358679197</v>
+        <v>-9.57798013586792</v>
       </c>
       <c r="C45">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3">
       <c r="A46">
         <v>26.752165863770749</v>
       </c>
@@ -3182,7 +2674,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3">
       <c r="A47">
         <v>25.068353463518633</v>
       </c>
@@ -3193,7 +2685,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3">
       <c r="A48">
         <v>23.384375985367875</v>
       </c>
@@ -3204,7 +2696,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3">
       <c r="A49">
         <v>21.701227324342735</v>
       </c>
@@ -3215,7 +2707,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3">
       <c r="A50">
         <v>20.018678621824527</v>
       </c>
@@ -3226,7 +2718,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3">
       <c r="A51">
         <v>18.336281557280227</v>
       </c>
@@ -3237,18 +2729,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3">
       <c r="A52">
         <v>16.653932716162338</v>
       </c>
       <c r="B52">
-        <v>-5.8633799854038697</v>
+        <v>-5.86337998540387</v>
       </c>
       <c r="C52">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3">
       <c r="A53">
         <v>14.971614910419747</v>
       </c>
@@ -3259,7 +2751,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3">
       <c r="A54">
         <v>13.289310952001358</v>
       </c>
@@ -3270,7 +2762,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3">
       <c r="A55">
         <v>11.607002478238378</v>
       </c>
@@ -3281,7 +2773,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3">
       <c r="A56">
         <v>9.9246664279913563</v>
       </c>
@@ -3292,9 +2784,9 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3">
       <c r="A57">
-        <v>8.2422785655031401</v>
+        <v>8.24227856550314</v>
       </c>
       <c r="B57">
         <v>-3.1996510759313788</v>
@@ -3303,7 +2795,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3">
       <c r="A58">
         <v>6.559814655016611</v>
       </c>
@@ -3314,7 +2806,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3">
       <c r="A59">
         <v>4.8772602844208857</v>
       </c>
@@ -3325,7 +2817,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3">
       <c r="A60">
         <v>3.1946403361902727</v>
       </c>
@@ -3336,18 +2828,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3">
       <c r="A61">
         <v>1.5119895164453261</v>
       </c>
       <c r="B61">
-        <v>-1.0717236149996729</v>
+        <v>-1.071723614999673</v>
       </c>
       <c r="C61">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3">
       <c r="A62">
         <v>-0.1706574686933697</v>
       </c>
@@ -3358,18 +2850,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3">
       <c r="A63">
         <v>-1.8532774818121083</v>
       </c>
       <c r="B63">
-        <v>-8.1474042927496843E-3</v>
+        <v>-0.0081474042927496843</v>
       </c>
       <c r="C63">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3">
       <c r="A64">
         <v>-3.5358936603246023</v>
       </c>
@@ -3380,7 +2872,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3">
       <c r="A65">
         <v>-5.2185407103514256</v>
       </c>
@@ -3391,7 +2883,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3">
       <c r="A66">
         <v>-6.9012533380131451</v>
       </c>
@@ -3402,7 +2894,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3">
       <c r="A67">
         <v>-8.584056425784043</v>
       </c>
@@ -3413,7 +2905,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3">
       <c r="A68">
         <v>-10.266935561553266</v>
       </c>
@@ -3424,7 +2916,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3">
       <c r="A69">
         <v>-11.949866509563682</v>
       </c>
@@ -3435,7 +2927,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3">
       <c r="A70">
         <v>-13.632825034058143</v>
       </c>
@@ -3446,7 +2938,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3">
       <c r="A71">
         <v>-15.31578807389719</v>
       </c>
@@ -3457,7 +2949,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3">
       <c r="A72">
         <v>-16.998737266412039</v>
       </c>
@@ -3468,7 +2960,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3">
       <c r="A73">
         <v>-18.681655423551582</v>
       </c>
@@ -3479,7 +2971,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3">
       <c r="A74">
         <v>-20.364525357264718</v>
       </c>
@@ -3490,7 +2982,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3">
       <c r="A75">
         <v>-22.04724365300395</v>
       </c>
@@ -3501,18 +2993,18 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3">
       <c r="A76">
         <v>-23.729361990236246</v>
       </c>
       <c r="B76">
-        <v>6.8992474723297397</v>
+        <v>6.89924747232974</v>
       </c>
       <c r="C76">
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3">
       <c r="A77">
         <v>-25.410651510342927</v>
       </c>
@@ -3523,7 +3015,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3">
       <c r="A78">
         <v>-27.092106108348254</v>
       </c>
@@ -3534,7 +3026,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3">
       <c r="A79">
         <v>-28.774669761625184</v>
       </c>
@@ -3545,7 +3037,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3">
       <c r="A80">
         <v>-30.457864023298413</v>
       </c>
@@ -3556,9 +3048,9 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3">
       <c r="A81">
-        <v>-32.140854840430599</v>
+        <v>-32.1408548404306</v>
       </c>
       <c r="B81">
         <v>9.5634867534386814</v>
@@ -3567,7 +3059,7 @@
         <v>270.8451733278763</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3">
       <c r="A82">
         <v>-33.822808160084357</v>
       </c>
